--- a/src/main/resources/doc/설문조사그룹리스트(가안)_240306_v0.9.xlsx
+++ b/src/main/resources/doc/설문조사그룹리스트(가안)_240306_v0.9.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20407"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\git\ponkids\src\main\resources\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4E13695-7D5E-4438-9A75-F074AF7E7C2F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AF3E40-63E0-4AE7-A06F-AEA51B094B82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="10860" windowHeight="3240" xr2:uid="{3A8A5E6F-AF63-4AB7-B9A0-177C4665B708}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="57">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -968,10 +968,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>문의 유형을 선택해주세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>피오니키즈관련
 수업관련문의
 강사관련문의
@@ -980,10 +976,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>문의내용을 입력하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>학부모 상담요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -992,25 +984,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>상단 안내문 (선택)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">선택지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하단 안내문 (선택)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>설문조사 그룹 
- - 필수 조건 : 로그인 한 대상자
+ - 로그인 하지 않아도 설문조사 가능하게 ( 제휴문의, 강사지원, 등 다양한 설문조사가 있음 )
  - 내용 검토 요청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>안내문(필수아님) 및 항목 요청</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상단 안내문 (선택)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">선택지 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>하단 안내문 (선택)</t>
+    <t>주관식( 장문 서술)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용 어떻게 채워야할지 요청드립니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문의 유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문의 제목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문의 내용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1120,7 +1128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1423,13 +1431,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1445,142 +1486,151 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1897,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F866D16E-9B2C-4064-B43B-9AB30A2E3359}">
-  <dimension ref="B2:J32"/>
+  <dimension ref="B2:J33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
@@ -1913,15 +1963,15 @@
   <sheetData>
     <row r="2" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:10" ht="111" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
+      <c r="B3" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="49"/>
     </row>
     <row r="4" spans="2:10" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
@@ -1935,476 +1985,494 @@
       </c>
     </row>
     <row r="5" spans="2:10" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="34"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="28"/>
+    </row>
+    <row r="8" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B8" s="34"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="28"/>
+    </row>
+    <row r="9" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B9" s="34"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="4">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="28"/>
+    </row>
+    <row r="10" spans="2:10" ht="132" x14ac:dyDescent="0.3">
+      <c r="B10" s="34"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="4">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="28"/>
+    </row>
+    <row r="11" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B11" s="34"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="4">
+        <v>6</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="28"/>
+    </row>
+    <row r="12" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="35"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="14">
+        <v>7</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="29"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B14" s="34"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B15" s="34"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="45"/>
+    </row>
+    <row r="16" spans="2:10" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="34"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="4">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="45"/>
+    </row>
+    <row r="17" spans="2:10" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="34"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="4">
+        <v>5</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="45"/>
+    </row>
+    <row r="18" spans="2:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="B18" s="34"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="4">
+        <v>6</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="45"/>
+    </row>
+    <row r="19" spans="2:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="B19" s="34"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="4">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="45"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="34"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="4">
+        <v>8</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="45"/>
+    </row>
+    <row r="21" spans="2:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="34"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="4">
+        <v>9</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="45"/>
+    </row>
+    <row r="22" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="35"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="14">
+        <v>10</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="46"/>
+    </row>
+    <row r="23" spans="2:10" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="53"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="14">
+        <v>2</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="52"/>
+    </row>
+    <row r="25" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="35"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="14">
+        <v>3</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="42" t="s">
+      <c r="G25" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="46"/>
+    </row>
+    <row r="26" spans="2:10" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="22">
-        <v>1</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B8" s="14"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6">
-        <v>3</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="15"/>
-    </row>
-    <row r="9" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B9" s="14"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" spans="2:10" ht="132" x14ac:dyDescent="0.3">
-      <c r="B10" s="14"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="15"/>
-    </row>
-    <row r="11" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B11" s="14"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6">
-        <v>6</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="15"/>
-    </row>
-    <row r="12" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="30"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32">
-        <v>7</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="34"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="27">
-        <v>1</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B14" s="14"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="6">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B15" s="14"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="6">
-        <v>3</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="2:10" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="14"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="6">
-        <v>4</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="2:10" ht="34.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="14"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="6">
-        <v>5</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="2:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="B18" s="14"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="6">
-        <v>6</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" spans="2:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="B19" s="14"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="6">
-        <v>7</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="14"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="6">
-        <v>8</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="21" spans="2:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="14"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="6">
-        <v>9</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="30"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="32">
-        <v>10</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="2:10" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="27">
-        <v>1</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I23" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="40" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="30"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="32">
-        <v>2</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="2:10" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="50"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="3"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="26"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C27" s="3"/>
@@ -2423,15 +2491,18 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="D26:J26"/>
     <mergeCell ref="J6:J12"/>
     <mergeCell ref="D6:D12"/>
     <mergeCell ref="B6:B12"/>

--- a/src/main/resources/doc/설문조사그룹리스트(가안)_240306_v0.9.xlsx
+++ b/src/main/resources/doc/설문조사그룹리스트(가안)_240306_v0.9.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\git\ponkids\src\main\resources\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjeoV/Desktop/jjeoV/2023/pioneerKids/workspace/ponkidsDev/ponkids/src/main/resources/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AF3E40-63E0-4AE7-A06F-AEA51B094B82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD96ABD-0676-5C4B-80AE-249D49F69782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10860" windowHeight="3240" xr2:uid="{3A8A5E6F-AF63-4AB7-B9A0-177C4665B708}"/>
+    <workbookView xWindow="3440" yWindow="3620" windowWidth="33360" windowHeight="16400" xr2:uid="{3A8A5E6F-AF63-4AB7-B9A0-177C4665B708}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -464,10 +464,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QESTNAR001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>코드(개발용)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -901,19 +897,6 @@
   </si>
   <si>
     <t>어린이를 대상으로 수업 해보신 경험이 있으신가요?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>안녕하세요, 유 · 초등 온라인 수업 라라클래스 입니다 :)
-라라클래스는 5-13세 어린이들이 놀이를 통해 성장할 수 있는 에듀테인먼트를 지향합니다.
-자신만의 특별한 수업을 만들고 싶은 강사님!
-국내~해외 유명 온라인 강사로 진출하고 싶은 강사님!
-커리큘럼 개발부터 모의 수업, 강의 진행까지 아이들을 가장 잘 아는 라라클래스가 멘토링 해드립니다.
-라라클래스에서 세상에 하나 뿐인 수업을 '함께' 만들어 보아요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>QESTNAR002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -960,10 +943,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QESTNAR003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:1 문의</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -980,10 +959,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QESTNAR004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>상단 안내문 (선택)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1019,6 +994,31 @@
   </si>
   <si>
     <t>문의 내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요, 유 · 초등 온라인 수업 라라클래스 입니다 :)
+피오니키즈는 5-13세 어린이들이 놀이를 통해 성장할 수 있는 에듀테인먼트를 지향합니다.
+자신만의 특별한 수업을 만들고 싶은 강사님!
+국내~해외 유명 온라인 강사로 진출하고 싶은 강사님!
+커리큘럼 개발부터 모의 수업, 강의 진행까지 아이들을 가장 잘 아는 피오니키즈가 멘토링 해드립니다.
+피오니키즈에서 세상에 하나 뿐인 수업을 '함께' 만들어 보아요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QESTN001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QESTN002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QESTN003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QESTN004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1026,7 +1026,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1470,7 +1470,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1480,9 +1480,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1546,6 +1543,42 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1576,18 +1609,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1597,40 +1624,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1947,561 +1944,535 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F866D16E-9B2C-4064-B43B-9AB30A2E3359}">
-  <dimension ref="B2:J33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.75" customWidth="1"/>
+    <col min="4" max="4" width="50.6640625" customWidth="1"/>
     <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="22.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.125" customWidth="1"/>
-    <col min="8" max="8" width="66.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="77.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="72.625" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" customWidth="1"/>
+    <col min="8" max="8" width="66.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="77.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="72.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:10" ht="111" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="47" t="s">
+    <row r="2" spans="2:10" ht="18" thickBot="1"/>
+    <row r="3" spans="2:10" ht="111" customHeight="1" thickBot="1">
+      <c r="B3" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26"/>
+    </row>
+    <row r="4" spans="2:10" ht="91" thickBot="1">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="B5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="18" thickTop="1">
+      <c r="B6" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="45"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="39"/>
+    </row>
+    <row r="8" spans="2:10" ht="18">
+      <c r="B8" s="45"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="39"/>
+    </row>
+    <row r="9" spans="2:10" ht="18">
+      <c r="B9" s="45"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="39"/>
+    </row>
+    <row r="10" spans="2:10" ht="144">
+      <c r="B10" s="45"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="39"/>
+    </row>
+    <row r="11" spans="2:10" ht="18">
+      <c r="B11" s="45"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="3">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="39"/>
+    </row>
+    <row r="12" spans="2:10" ht="19" thickBot="1">
+      <c r="B12" s="35"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="13">
+        <v>7</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="40"/>
+    </row>
+    <row r="13" spans="2:10" ht="18">
+      <c r="B13" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="18">
+      <c r="B14" s="45"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="52"/>
+    </row>
+    <row r="15" spans="2:10" ht="18">
+      <c r="B15" s="45"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="3">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="52"/>
+    </row>
+    <row r="16" spans="2:10" ht="90">
+      <c r="B16" s="45"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="3">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="52"/>
+    </row>
+    <row r="17" spans="2:10" ht="38">
+      <c r="B17" s="45"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="3">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="52"/>
+    </row>
+    <row r="18" spans="2:10" ht="36">
+      <c r="B18" s="45"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="3">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="52"/>
+    </row>
+    <row r="19" spans="2:10" ht="72">
+      <c r="B19" s="45"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="3">
+        <v>7</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="52"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="45"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="3">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="52"/>
+    </row>
+    <row r="21" spans="2:10" ht="54">
+      <c r="B21" s="45"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="3">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="52"/>
+    </row>
+    <row r="22" spans="2:10" ht="18" thickBot="1">
+      <c r="B22" s="35"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="13">
+        <v>10</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="32"/>
+    </row>
+    <row r="23" spans="2:10" ht="90">
+      <c r="B23" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="11">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="18" thickBot="1">
+      <c r="B24" s="34"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="13">
+        <v>2</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" spans="2:10" ht="18" thickBot="1">
+      <c r="B25" s="35"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="13">
+        <v>3</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
+      <c r="I25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="32"/>
     </row>
-    <row r="4" spans="2:10" ht="83.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="21" t="s">
+    <row r="26" spans="2:10" ht="38" thickBot="1">
+      <c r="B26" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="11">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="34"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="4">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="28"/>
-    </row>
-    <row r="8" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B8" s="34"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="4">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="28"/>
-    </row>
-    <row r="9" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B9" s="34"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="4">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" spans="2:10" ht="132" x14ac:dyDescent="0.3">
-      <c r="B10" s="34"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="4">
-        <v>5</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" s="28"/>
-    </row>
-    <row r="11" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B11" s="34"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="4">
-        <v>6</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="28"/>
-    </row>
-    <row r="12" spans="2:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="35"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="14">
-        <v>7</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="29"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="12">
-        <v>1</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B14" s="34"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="4">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="45"/>
-    </row>
-    <row r="15" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B15" s="34"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="4">
-        <v>3</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="45"/>
-    </row>
-    <row r="16" spans="2:10" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="34"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="4">
-        <v>4</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="45"/>
-    </row>
-    <row r="17" spans="2:10" ht="34.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="34"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="4">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="45"/>
-    </row>
-    <row r="18" spans="2:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="B18" s="34"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="4">
-        <v>6</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="45"/>
-    </row>
-    <row r="19" spans="2:10" ht="66" x14ac:dyDescent="0.3">
-      <c r="B19" s="34"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="4">
-        <v>7</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J19" s="45"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="34"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="4">
-        <v>8</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="45"/>
-    </row>
-    <row r="21" spans="2:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B21" s="34"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="4">
-        <v>9</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J21" s="45"/>
-    </row>
-    <row r="22" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="35"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="14">
-        <v>10</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="46"/>
-    </row>
-    <row r="23" spans="2:10" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B23" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="53"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="14">
-        <v>2</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="52"/>
-    </row>
-    <row r="25" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="35"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="14">
-        <v>3</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="46"/>
-    </row>
-    <row r="26" spans="2:10" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="3"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="J23:J25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="B23:B25"/>
     <mergeCell ref="D26:J26"/>
     <mergeCell ref="J6:J12"/>
     <mergeCell ref="D6:D12"/>
@@ -2511,6 +2482,11 @@
     <mergeCell ref="C13:C22"/>
     <mergeCell ref="B13:B22"/>
     <mergeCell ref="J13:J22"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="B23:B25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
